--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/170.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/170.xlsx
@@ -426,13 +426,13 @@
         <v>-14.01677135551921</v>
       </c>
       <c r="E2">
-        <v>-7.397404750931369</v>
+        <v>-6.457329774731064</v>
       </c>
       <c r="F2">
-        <v>-4.177136381380532</v>
+        <v>-4.698665729406864</v>
       </c>
       <c r="G2">
-        <v>-2.626435696431287</v>
+        <v>-1.650880826373315</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.09858496362666</v>
       </c>
       <c r="E3">
-        <v>-7.403527247789739</v>
+        <v>-7.922694150399107</v>
       </c>
       <c r="F3">
-        <v>-5.300444826314203</v>
+        <v>-5.113692708822666</v>
       </c>
       <c r="G3">
-        <v>-2.21479253244169</v>
+        <v>-2.253340524700964</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.02776277623341</v>
       </c>
       <c r="E4">
-        <v>-7.67509983402973</v>
+        <v>-7.426794547241149</v>
       </c>
       <c r="F4">
-        <v>-4.328116280949574</v>
+        <v>-4.944189685759623</v>
       </c>
       <c r="G4">
-        <v>-2.606926651568362</v>
+        <v>-2.343605859374732</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.80031499764404</v>
       </c>
       <c r="E5">
-        <v>-9.182891482675638</v>
+        <v>-8.976981769546866</v>
       </c>
       <c r="F5">
-        <v>-4.663671348475598</v>
+        <v>-5.211710938493724</v>
       </c>
       <c r="G5">
-        <v>-1.883559209055451</v>
+        <v>-2.052122256278522</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.4237225597139</v>
       </c>
       <c r="E6">
-        <v>-9.525117320383302</v>
+        <v>-10.64452892423537</v>
       </c>
       <c r="F6">
-        <v>-4.475600470078804</v>
+        <v>-4.914901099498841</v>
       </c>
       <c r="G6">
-        <v>-1.239846802762943</v>
+        <v>-1.403881023688291</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.91745182277021</v>
       </c>
       <c r="E7">
-        <v>-9.852770528734283</v>
+        <v>-10.19458880378126</v>
       </c>
       <c r="F7">
-        <v>-4.805212001489742</v>
+        <v>-4.826553230888065</v>
       </c>
       <c r="G7">
-        <v>-2.045961331029938</v>
+        <v>-1.572831404739457</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.30740471321875</v>
       </c>
       <c r="E8">
-        <v>-12.10202734055209</v>
+        <v>-12.26358970772374</v>
       </c>
       <c r="F8">
-        <v>-4.626120625739294</v>
+        <v>-4.703584575044687</v>
       </c>
       <c r="G8">
-        <v>-1.942771626570855</v>
+        <v>-1.554808794823665</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.60591942481224</v>
       </c>
       <c r="E9">
-        <v>-11.28419399171484</v>
+        <v>-13.11181817410048</v>
       </c>
       <c r="F9">
-        <v>-4.796244095987034</v>
+        <v>-4.891237127903067</v>
       </c>
       <c r="G9">
-        <v>-1.474216874215647</v>
+        <v>-1.237105671056427</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.83332267047241</v>
       </c>
       <c r="E10">
-        <v>-12.41414335458275</v>
+        <v>-13.2810336623451</v>
       </c>
       <c r="F10">
-        <v>-4.451670592546732</v>
+        <v>-4.768469765338569</v>
       </c>
       <c r="G10">
-        <v>-0.7379085091897244</v>
+        <v>-0.8738659933965135</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.02264382181367</v>
       </c>
       <c r="E11">
-        <v>-14.37187965215678</v>
+        <v>-14.39475297436952</v>
       </c>
       <c r="F11">
-        <v>-4.457119593322347</v>
+        <v>-4.893004863940641</v>
       </c>
       <c r="G11">
-        <v>-0.132320345327464</v>
+        <v>-0.6365230520495443</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.19361706984667</v>
       </c>
       <c r="E12">
-        <v>-14.31579903004579</v>
+        <v>-15.62238605005689</v>
       </c>
       <c r="F12">
-        <v>-4.362061120381493</v>
+        <v>-4.973996001647155</v>
       </c>
       <c r="G12">
-        <v>-0.2180965802499804</v>
+        <v>-0.4017226096767354</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.368671380127465</v>
       </c>
       <c r="E13">
-        <v>-16.58225045767072</v>
+        <v>-16.01373224532576</v>
       </c>
       <c r="F13">
-        <v>-4.891658766911092</v>
+        <v>-4.93939509523222</v>
       </c>
       <c r="G13">
-        <v>0.2449262505091056</v>
+        <v>0.58558469704565</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.589480222780854</v>
       </c>
       <c r="E14">
-        <v>-16.82007685560555</v>
+        <v>-17.0245555709479</v>
       </c>
       <c r="F14">
-        <v>-4.692505989399646</v>
+        <v>-4.44385825957093</v>
       </c>
       <c r="G14">
-        <v>1.611850503674179</v>
+        <v>1.426330842198961</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.877543520772519</v>
       </c>
       <c r="E15">
-        <v>-18.03473585326095</v>
+        <v>-17.65549879748859</v>
       </c>
       <c r="F15">
-        <v>-4.688089962775322</v>
+        <v>-4.647813911283808</v>
       </c>
       <c r="G15">
-        <v>1.858039222702081</v>
+        <v>1.884990373937287</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.248726404913602</v>
       </c>
       <c r="E16">
-        <v>-17.68643280343499</v>
+        <v>-18.73364694618277</v>
       </c>
       <c r="F16">
-        <v>-4.059610099373546</v>
+        <v>-4.513378993850878</v>
       </c>
       <c r="G16">
-        <v>2.20971516479332</v>
+        <v>2.192934009454754</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.728117748096926</v>
       </c>
       <c r="E17">
-        <v>-19.23346367935736</v>
+        <v>-20.10719198287129</v>
       </c>
       <c r="F17">
-        <v>-4.304958441836912</v>
+        <v>-4.392709885917672</v>
       </c>
       <c r="G17">
-        <v>4.035378402789662</v>
+        <v>3.299940711240568</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.317233727796006</v>
       </c>
       <c r="E18">
-        <v>-20.59710947186511</v>
+        <v>-20.96458608063955</v>
       </c>
       <c r="F18">
-        <v>-4.041107685064616</v>
+        <v>-3.892246749311933</v>
       </c>
       <c r="G18">
-        <v>3.291730558303175</v>
+        <v>3.656817520374001</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.006882011207177</v>
       </c>
       <c r="E19">
-        <v>-19.71377627498092</v>
+        <v>-21.89922688803065</v>
       </c>
       <c r="F19">
-        <v>-3.373666389239567</v>
+        <v>-4.196670113105946</v>
       </c>
       <c r="G19">
-        <v>4.106767006798505</v>
+        <v>3.27221820289471</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.795297877067913</v>
       </c>
       <c r="E20">
-        <v>-21.99734080588083</v>
+        <v>-22.82455262438797</v>
       </c>
       <c r="F20">
-        <v>-3.558721181922769</v>
+        <v>-3.812176756157333</v>
       </c>
       <c r="G20">
-        <v>4.323220405792673</v>
+        <v>5.045942291925427</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.667457362622356</v>
       </c>
       <c r="E21">
-        <v>-22.51548427336446</v>
+        <v>-23.94560353583081</v>
       </c>
       <c r="F21">
-        <v>-3.567556548641028</v>
+        <v>-3.585288581265354</v>
       </c>
       <c r="G21">
-        <v>4.691604671220614</v>
+        <v>4.945007068978588</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.601970168480737</v>
       </c>
       <c r="E22">
-        <v>-22.99534402158725</v>
+        <v>-24.08295215248345</v>
       </c>
       <c r="F22">
-        <v>-3.377267302339537</v>
+        <v>-3.441599971575752</v>
       </c>
       <c r="G22">
-        <v>5.145384458834055</v>
+        <v>5.257184892240782</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.588408222434234</v>
       </c>
       <c r="E23">
-        <v>-22.99644896924513</v>
+        <v>-24.16654325419104</v>
       </c>
       <c r="F23">
-        <v>-3.337335851687587</v>
+        <v>-2.968039723110734</v>
       </c>
       <c r="G23">
-        <v>5.173209594091629</v>
+        <v>4.590778696276571</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.612755702429891</v>
       </c>
       <c r="E24">
-        <v>-24.5943753645397</v>
+        <v>-25.04746277442915</v>
       </c>
       <c r="F24">
-        <v>-2.886227673308046</v>
+        <v>-3.597025718995621</v>
       </c>
       <c r="G24">
-        <v>4.863107482882558</v>
+        <v>5.304095322532255</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.656594946886417</v>
       </c>
       <c r="E25">
-        <v>-25.46108906181575</v>
+        <v>-25.45079584039631</v>
       </c>
       <c r="F25">
-        <v>-2.658381905698431</v>
+        <v>-2.927718111412065</v>
       </c>
       <c r="G25">
-        <v>4.733075875191064</v>
+        <v>5.277269972027541</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.712814163670608</v>
       </c>
       <c r="E26">
-        <v>-25.66543645141187</v>
+        <v>-25.08975419318678</v>
       </c>
       <c r="F26">
-        <v>-2.720104389248425</v>
+        <v>-3.172398789748774</v>
       </c>
       <c r="G26">
-        <v>5.258068807899768</v>
+        <v>4.987981260623867</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.776461079780693</v>
       </c>
       <c r="E27">
-        <v>-24.17333143672854</v>
+        <v>-25.30857458571142</v>
       </c>
       <c r="F27">
-        <v>-2.374890557805759</v>
+        <v>-3.059657986227762</v>
       </c>
       <c r="G27">
-        <v>4.454096202596681</v>
+        <v>5.06491502841099</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.838086060766267</v>
       </c>
       <c r="E28">
-        <v>-24.89756575630125</v>
+        <v>-24.58036426595997</v>
       </c>
       <c r="F28">
-        <v>-2.402649977840973</v>
+        <v>-3.190199576867533</v>
       </c>
       <c r="G28">
-        <v>3.56084480519053</v>
+        <v>4.783124702653766</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.898905137885166</v>
       </c>
       <c r="E29">
-        <v>-25.2851850174618</v>
+        <v>-24.26709801953136</v>
       </c>
       <c r="F29">
-        <v>-2.312253556643074</v>
+        <v>-3.011024536009403</v>
       </c>
       <c r="G29">
-        <v>4.670883966690316</v>
+        <v>5.019305642516451</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.964334874529161</v>
       </c>
       <c r="E30">
-        <v>-24.95398601396282</v>
+        <v>-24.95119647397409</v>
       </c>
       <c r="F30">
-        <v>-2.107441373035702</v>
+        <v>-3.032813083805238</v>
       </c>
       <c r="G30">
-        <v>3.845677522298344</v>
+        <v>4.237699082876681</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.032119589428534</v>
       </c>
       <c r="E31">
-        <v>-24.05319554977905</v>
+        <v>-23.70061309201584</v>
       </c>
       <c r="F31">
-        <v>-2.354704072566938</v>
+        <v>-2.558515588351728</v>
       </c>
       <c r="G31">
-        <v>3.361142766625074</v>
+        <v>3.352118219485021</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.108719306373695</v>
       </c>
       <c r="E32">
-        <v>-23.77329962831296</v>
+        <v>-23.45438637479678</v>
       </c>
       <c r="F32">
-        <v>-2.23897037761961</v>
+        <v>-2.90888269340721</v>
       </c>
       <c r="G32">
-        <v>4.067914444349619</v>
+        <v>3.77033612691561</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.204243390865226</v>
       </c>
       <c r="E33">
-        <v>-23.05179145009287</v>
+        <v>-23.64423359062035</v>
       </c>
       <c r="F33">
-        <v>-2.604122184080258</v>
+        <v>-3.132222970712998</v>
       </c>
       <c r="G33">
-        <v>3.940398851267971</v>
+        <v>3.599856273825301</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.31652879252311</v>
       </c>
       <c r="E34">
-        <v>-22.73686778217745</v>
+        <v>-22.55651224787396</v>
       </c>
       <c r="F34">
-        <v>-2.379183157687066</v>
+        <v>-2.981820443223706</v>
       </c>
       <c r="G34">
-        <v>3.401852545121492</v>
+        <v>3.415409229104807</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.449608684617284</v>
       </c>
       <c r="E35">
-        <v>-22.4808459756798</v>
+        <v>-22.41634692038854</v>
       </c>
       <c r="F35">
-        <v>-2.268803201264032</v>
+        <v>-2.861965620447451</v>
       </c>
       <c r="G35">
-        <v>2.671423708973315</v>
+        <v>3.384968762871209</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.609755325727638</v>
       </c>
       <c r="E36">
-        <v>-21.69400097447703</v>
+        <v>-22.41237544868382</v>
       </c>
       <c r="F36">
-        <v>-2.687605879301795</v>
+        <v>-2.904724289045156</v>
       </c>
       <c r="G36">
-        <v>3.88121953920796</v>
+        <v>2.762377637119251</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.7906929756377</v>
       </c>
       <c r="E37">
-        <v>-20.94269543728647</v>
+        <v>-20.47605883316607</v>
       </c>
       <c r="F37">
-        <v>-2.272143178632119</v>
+        <v>-2.73136190225247</v>
       </c>
       <c r="G37">
-        <v>2.635381799687269</v>
+        <v>2.665934824469203</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.989815300863064</v>
       </c>
       <c r="E38">
-        <v>-19.52018401115301</v>
+        <v>-20.52464483079437</v>
       </c>
       <c r="F38">
-        <v>-2.281937794802821</v>
+        <v>-2.53250982210824</v>
       </c>
       <c r="G38">
-        <v>2.232392401737327</v>
+        <v>2.458535767524942</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.21001909210531</v>
       </c>
       <c r="E39">
-        <v>-20.03069247145971</v>
+        <v>-19.21408633907854</v>
       </c>
       <c r="F39">
-        <v>-2.162198943462958</v>
+        <v>-2.167141811755462</v>
       </c>
       <c r="G39">
-        <v>2.831975235991349</v>
+        <v>2.558990961368587</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.444783192611637</v>
       </c>
       <c r="E40">
-        <v>-18.4955035550674</v>
+        <v>-19.37984207318129</v>
       </c>
       <c r="F40">
-        <v>-2.776203914868216</v>
+        <v>-2.292171445697006</v>
       </c>
       <c r="G40">
-        <v>2.422603106241692</v>
+        <v>2.323280118972478</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.688833599201785</v>
       </c>
       <c r="E41">
-        <v>-17.65264133038975</v>
+        <v>-17.40034192952641</v>
       </c>
       <c r="F41">
-        <v>-2.130302656618163</v>
+        <v>-2.339156444783794</v>
       </c>
       <c r="G41">
-        <v>2.04141696121339</v>
+        <v>2.40535185343655</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.945850363423745</v>
       </c>
       <c r="E42">
-        <v>-17.45226088402435</v>
+        <v>-17.09414463102377</v>
       </c>
       <c r="F42">
-        <v>-2.441356273104183</v>
+        <v>-2.369675156637733</v>
       </c>
       <c r="G42">
-        <v>2.351111875321131</v>
+        <v>2.083103350643893</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.21242213182976</v>
       </c>
       <c r="E43">
-        <v>-17.21693873221576</v>
+        <v>-17.46670218763481</v>
       </c>
       <c r="F43">
-        <v>-2.523136844945564</v>
+        <v>-2.126304955532252</v>
       </c>
       <c r="G43">
-        <v>2.476316707616367</v>
+        <v>2.219789154869322</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.481967873660681</v>
       </c>
       <c r="E44">
-        <v>-15.59206338810153</v>
+        <v>-16.15891965048568</v>
       </c>
       <c r="F44">
-        <v>-1.839811604171835</v>
+        <v>-2.110445861605656</v>
       </c>
       <c r="G44">
-        <v>2.105462775216131</v>
+        <v>1.766750929456678</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.758440636200135</v>
       </c>
       <c r="E45">
-        <v>-14.83038311695939</v>
+        <v>-14.61036720729673</v>
       </c>
       <c r="F45">
-        <v>-2.04196141494661</v>
+        <v>-2.059582446338961</v>
       </c>
       <c r="G45">
-        <v>2.180969697875828</v>
+        <v>1.802931881655372</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.041074681260138</v>
       </c>
       <c r="E46">
-        <v>-14.37535299172066</v>
+        <v>-13.20170838315273</v>
       </c>
       <c r="F46">
-        <v>-1.976431754813349</v>
+        <v>-1.799118883876712</v>
       </c>
       <c r="G46">
-        <v>2.407424254944134</v>
+        <v>1.76960130916599</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.321357016805843</v>
       </c>
       <c r="E47">
-        <v>-12.61440606062396</v>
+        <v>-13.59129300203261</v>
       </c>
       <c r="F47">
-        <v>-1.766677531280875</v>
+        <v>-1.782558162759944</v>
       </c>
       <c r="G47">
-        <v>2.241887046343957</v>
+        <v>1.058353773872351</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.603370289367032</v>
       </c>
       <c r="E48">
-        <v>-13.80226102062795</v>
+        <v>-12.7662186232571</v>
       </c>
       <c r="F48">
-        <v>-1.455934552570905</v>
+        <v>-1.954759178453906</v>
       </c>
       <c r="G48">
-        <v>1.626188476404762</v>
+        <v>0.338856359094847</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.889407092552545</v>
       </c>
       <c r="E49">
-        <v>-11.88412622825101</v>
+        <v>-11.39403212877088</v>
       </c>
       <c r="F49">
-        <v>-1.697619854379091</v>
+        <v>-1.961506230949708</v>
       </c>
       <c r="G49">
-        <v>1.984177628839391</v>
+        <v>1.461462351461706</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.169392763739904</v>
       </c>
       <c r="E50">
-        <v>-9.946931088775772</v>
+        <v>-9.295759168842814</v>
       </c>
       <c r="F50">
-        <v>-1.807985728556278</v>
+        <v>-1.730498584963607</v>
       </c>
       <c r="G50">
-        <v>1.76624110544363</v>
+        <v>0.8765816499475874</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.445923949805742</v>
       </c>
       <c r="E51">
-        <v>-11.17196029190873</v>
+        <v>-10.6861093725738</v>
       </c>
       <c r="F51">
-        <v>-2.09119294642979</v>
+        <v>-1.770219630295246</v>
       </c>
       <c r="G51">
-        <v>1.240245077436527</v>
+        <v>0.3663471292529549</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.723854885039721</v>
       </c>
       <c r="E52">
-        <v>-8.011185060982994</v>
+        <v>-9.302923214722947</v>
       </c>
       <c r="F52">
-        <v>-1.635308401605707</v>
+        <v>-1.614037583436621</v>
       </c>
       <c r="G52">
-        <v>1.422854769382726</v>
+        <v>0.1884880701556104</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.990989347044371</v>
       </c>
       <c r="E53">
-        <v>-8.203310099232416</v>
+        <v>-7.661573282168819</v>
       </c>
       <c r="F53">
-        <v>-1.558791276241714</v>
+        <v>-1.380530752996274</v>
       </c>
       <c r="G53">
-        <v>1.425814397094834</v>
+        <v>0.2727348330389835</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.24683198583817</v>
       </c>
       <c r="E54">
-        <v>-8.986554963599081</v>
+        <v>-7.528685212413732</v>
       </c>
       <c r="F54">
-        <v>-1.628186098676437</v>
+        <v>-1.561799906648682</v>
       </c>
       <c r="G54">
-        <v>0.3243495485417606</v>
+        <v>0.02593035254077729</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.49551701125198</v>
       </c>
       <c r="E55">
-        <v>-7.400425243094484</v>
+        <v>-7.261428261903051</v>
       </c>
       <c r="F55">
-        <v>-1.554678432086814</v>
+        <v>-1.68563254969318</v>
       </c>
       <c r="G55">
-        <v>-0.06070662422194967</v>
+        <v>-0.5178333733755938</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.72318955433877</v>
       </c>
       <c r="E56">
-        <v>-6.955009068174036</v>
+        <v>-5.579593771720349</v>
       </c>
       <c r="F56">
-        <v>-1.767041184570704</v>
+        <v>-1.652314784385181</v>
       </c>
       <c r="G56">
-        <v>-0.7054618523593276</v>
+        <v>-0.6496195702029012</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.92289645861898</v>
       </c>
       <c r="E57">
-        <v>-7.107980920153141</v>
+        <v>-5.367430235986985</v>
       </c>
       <c r="F57">
-        <v>-1.577272981365574</v>
+        <v>-1.911360181853837</v>
       </c>
       <c r="G57">
-        <v>-0.8368110571754511</v>
+        <v>-0.4976224928583431</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.09536506795203</v>
       </c>
       <c r="E58">
-        <v>-5.882109420854752</v>
+        <v>-4.822360462053743</v>
       </c>
       <c r="F58">
-        <v>-1.679381689271655</v>
+        <v>-1.437186113143344</v>
       </c>
       <c r="G58">
-        <v>-0.5949392895307589</v>
+        <v>-0.540543715774994</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.22791883814645</v>
       </c>
       <c r="E59">
-        <v>-4.55407554794332</v>
+        <v>-4.488933449342982</v>
       </c>
       <c r="F59">
-        <v>-2.116355434657228</v>
+        <v>-1.250398375853486</v>
       </c>
       <c r="G59">
-        <v>-1.026058392927889</v>
+        <v>-0.4892004650064372</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.31011494190195</v>
       </c>
       <c r="E60">
-        <v>-4.011654931304564</v>
+        <v>-3.92788269063667</v>
       </c>
       <c r="F60">
-        <v>-1.682169145582075</v>
+        <v>-1.547658018348089</v>
       </c>
       <c r="G60">
-        <v>-1.151144045583711</v>
+        <v>-1.130956338885235</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.34460351602457</v>
       </c>
       <c r="E61">
-        <v>-3.530441169353482</v>
+        <v>-3.655522149919344</v>
       </c>
       <c r="F61">
-        <v>-1.623226663035876</v>
+        <v>-1.751985607024823</v>
       </c>
       <c r="G61">
-        <v>-0.6363939407735127</v>
+        <v>-1.011528408556027</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.32678520571772</v>
       </c>
       <c r="E62">
-        <v>-3.514111492081822</v>
+        <v>-2.708405396637112</v>
       </c>
       <c r="F62">
-        <v>-1.771819207750051</v>
+        <v>-1.513545848700805</v>
       </c>
       <c r="G62">
-        <v>-1.538736096230503</v>
+        <v>-1.503124557864563</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.25018003087863</v>
       </c>
       <c r="E63">
-        <v>-4.964409634726346</v>
+        <v>-2.87834091224895</v>
       </c>
       <c r="F63">
-        <v>-1.94139181367493</v>
+        <v>-1.673225262734049</v>
       </c>
       <c r="G63">
-        <v>-0.7723514249803018</v>
+        <v>-1.644872186219537</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.12189791297163</v>
       </c>
       <c r="E64">
-        <v>-4.074845257607596</v>
+        <v>-1.768475331605053</v>
       </c>
       <c r="F64">
-        <v>-1.483808287307705</v>
+        <v>-1.852448348901541</v>
       </c>
       <c r="G64">
-        <v>-1.017523806527648</v>
+        <v>-0.9184987683569676</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.94506549795123</v>
       </c>
       <c r="E65">
-        <v>-3.171450920869422</v>
+        <v>-2.729548841778925</v>
       </c>
       <c r="F65">
-        <v>-1.832688472875162</v>
+        <v>-1.697826946229791</v>
       </c>
       <c r="G65">
-        <v>-1.623383435124128</v>
+        <v>-1.32916532141248</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.71561407140707</v>
       </c>
       <c r="E66">
-        <v>-3.552540122510913</v>
+        <v>-2.033717111182321</v>
       </c>
       <c r="F66">
-        <v>-1.835540541843001</v>
+        <v>-1.920347968174211</v>
       </c>
       <c r="G66">
-        <v>-0.613044663085033</v>
+        <v>-0.917257313779741</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.44122128925883</v>
       </c>
       <c r="E67">
-        <v>-2.25903133543396</v>
+        <v>-2.228129028805617</v>
       </c>
       <c r="F67">
-        <v>-1.399757160415251</v>
+        <v>-1.767342710305323</v>
       </c>
       <c r="G67">
-        <v>-1.662696163402974</v>
+        <v>-1.26107402076075</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.13081023368583</v>
       </c>
       <c r="E68">
-        <v>-2.745792478044439</v>
+        <v>-1.193952362725922</v>
       </c>
       <c r="F68">
-        <v>-2.037211556258957</v>
+        <v>-1.907512415267833</v>
       </c>
       <c r="G68">
-        <v>-2.391727949333578</v>
+        <v>-0.8414458209304307</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.782683586281177</v>
       </c>
       <c r="E69">
-        <v>-3.20096298597741</v>
+        <v>-2.710819073283201</v>
       </c>
       <c r="F69">
-        <v>-1.939728451930109</v>
+        <v>-1.470240457617252</v>
       </c>
       <c r="G69">
-        <v>-0.8773486873038269</v>
+        <v>-0.7196442294495653</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.402498205002326</v>
       </c>
       <c r="E70">
-        <v>-1.384429036436553</v>
+        <v>-2.575032780163205</v>
       </c>
       <c r="F70">
-        <v>-1.684203615923351</v>
+        <v>-1.954861896011853</v>
       </c>
       <c r="G70">
-        <v>-1.797478403943321</v>
+        <v>-0.6953514462823933</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.002668256795886</v>
       </c>
       <c r="E71">
-        <v>-1.154450483957014</v>
+        <v>-2.000550567550143</v>
       </c>
       <c r="F71">
-        <v>-2.436151640712394</v>
+        <v>-1.706075000459466</v>
       </c>
       <c r="G71">
-        <v>-1.871336674924462</v>
+        <v>0.1176887432527568</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.582189701521839</v>
       </c>
       <c r="E72">
-        <v>-2.051876291953079</v>
+        <v>-1.573180361550261</v>
       </c>
       <c r="F72">
-        <v>-2.092588745503507</v>
+        <v>-2.148690756225506</v>
       </c>
       <c r="G72">
-        <v>-0.9308007555808994</v>
+        <v>-0.4845292852505256</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.141651500118067</v>
       </c>
       <c r="E73">
-        <v>-3.488575427152569</v>
+        <v>-2.107635392409525</v>
       </c>
       <c r="F73">
-        <v>-2.149634266697295</v>
+        <v>-1.909578363570415</v>
       </c>
       <c r="G73">
-        <v>-0.9224648019130146</v>
+        <v>-0.4236847687842604</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.693724663591725</v>
       </c>
       <c r="E74">
-        <v>-3.582111057781</v>
+        <v>-1.724707630320919</v>
       </c>
       <c r="F74">
-        <v>-1.968637645920408</v>
+        <v>-2.184049618814003</v>
       </c>
       <c r="G74">
-        <v>-0.3277352274195636</v>
+        <v>0.8302902916719583</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.236149311728191</v>
       </c>
       <c r="E75">
-        <v>-2.304560613107077</v>
+        <v>-2.103156731615938</v>
       </c>
       <c r="F75">
-        <v>-2.32354668944544</v>
+        <v>-2.018019111903495</v>
       </c>
       <c r="G75">
-        <v>0.02374870303039758</v>
+        <v>1.278654026783152</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.765608503405886</v>
       </c>
       <c r="E76">
-        <v>-2.952879594415204</v>
+        <v>-2.499552175403355</v>
       </c>
       <c r="F76">
-        <v>-2.160142935569209</v>
+        <v>-2.449680537134915</v>
       </c>
       <c r="G76">
-        <v>0.4983915486323255</v>
+        <v>0.9883092513524506</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.291570465915948</v>
       </c>
       <c r="E77">
-        <v>-4.499670461215168</v>
+        <v>-4.298515645794451</v>
       </c>
       <c r="F77">
-        <v>-2.432089326969065</v>
+        <v>-2.571124168589739</v>
       </c>
       <c r="G77">
-        <v>0.484248898088559</v>
+        <v>1.311084130885852</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.813042727995928</v>
       </c>
       <c r="E78">
-        <v>-5.35136321020777</v>
+        <v>-4.561298463985554</v>
       </c>
       <c r="F78">
-        <v>-2.193692643749992</v>
+        <v>-2.674993985594172</v>
       </c>
       <c r="G78">
-        <v>0.9244720017186844</v>
+        <v>1.757680034679074</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.327478875493092</v>
       </c>
       <c r="E79">
-        <v>-6.328888666451509</v>
+        <v>-5.120786899159219</v>
       </c>
       <c r="F79">
-        <v>-2.575996625653006</v>
+        <v>-3.001535587410334</v>
       </c>
       <c r="G79">
-        <v>1.563804556262736</v>
+        <v>2.687082589374068</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.846116441780698</v>
       </c>
       <c r="E80">
-        <v>-6.584507438762478</v>
+        <v>-5.438939369042108</v>
       </c>
       <c r="F80">
-        <v>-2.600039989519261</v>
+        <v>-3.02371181115068</v>
       </c>
       <c r="G80">
-        <v>1.708991841433013</v>
+        <v>1.959967609310701</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.375805092504429</v>
       </c>
       <c r="E81">
-        <v>-7.290763716524739</v>
+        <v>-6.535174242922917</v>
       </c>
       <c r="F81">
-        <v>-2.639630981168661</v>
+        <v>-2.498637050640366</v>
       </c>
       <c r="G81">
-        <v>2.019987799937688</v>
+        <v>2.82684057985994</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.921567119404109</v>
       </c>
       <c r="E82">
-        <v>-9.101175169207226</v>
+        <v>-7.138335281426555</v>
       </c>
       <c r="F82">
-        <v>-2.765131127794995</v>
+        <v>-2.732104947812781</v>
       </c>
       <c r="G82">
-        <v>1.993281629072387</v>
+        <v>3.606123136531142</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.499602147144677</v>
       </c>
       <c r="E83">
-        <v>-10.38591230213132</v>
+        <v>-7.56457336892452</v>
       </c>
       <c r="F83">
-        <v>-2.851748536901322</v>
+        <v>-3.110849434985965</v>
       </c>
       <c r="G83">
-        <v>2.659379944301446</v>
+        <v>3.372385379276439</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.124051422068587</v>
       </c>
       <c r="E84">
-        <v>-12.06915514773041</v>
+        <v>-9.54871972691128</v>
       </c>
       <c r="F84">
-        <v>-3.183636421935153</v>
+        <v>-3.283085242110845</v>
       </c>
       <c r="G84">
-        <v>2.587243157000727</v>
+        <v>4.682298727709723</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.803674869460359</v>
       </c>
       <c r="E85">
-        <v>-11.94212239486724</v>
+        <v>-10.05706810511632</v>
       </c>
       <c r="F85">
-        <v>-3.25553291392633</v>
+        <v>-3.226927730772858</v>
       </c>
       <c r="G85">
-        <v>2.651931216838086</v>
+        <v>4.225499722564467</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.554355603740602</v>
       </c>
       <c r="E86">
-        <v>-11.75321257316326</v>
+        <v>-11.46434574468798</v>
       </c>
       <c r="F86">
-        <v>-2.868533745584248</v>
+        <v>-3.376878798027624</v>
       </c>
       <c r="G86">
-        <v>3.206470768484785</v>
+        <v>4.165400078844538</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.390313384917723</v>
       </c>
       <c r="E87">
-        <v>-12.84490538761438</v>
+        <v>-12.33354104572023</v>
       </c>
       <c r="F87">
-        <v>-3.662813829758555</v>
+        <v>-3.728274735397383</v>
       </c>
       <c r="G87">
-        <v>4.147106004194525</v>
+        <v>5.001948452254052</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.315765973523466</v>
       </c>
       <c r="E88">
-        <v>-14.57181630806943</v>
+        <v>-14.80701166260581</v>
       </c>
       <c r="F88">
-        <v>-3.912769551716291</v>
+        <v>-3.431165855770089</v>
       </c>
       <c r="G88">
-        <v>3.025436896215279</v>
+        <v>5.078342601118274</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.340562994812149</v>
       </c>
       <c r="E89">
-        <v>-16.20167297359209</v>
+        <v>-15.51968478803694</v>
       </c>
       <c r="F89">
-        <v>-3.608315538328375</v>
+        <v>-3.800452043938109</v>
       </c>
       <c r="G89">
-        <v>3.855811102194053</v>
+        <v>5.027022524168492</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.472974591974701</v>
       </c>
       <c r="E90">
-        <v>-17.21834708763214</v>
+        <v>-18.16897793674433</v>
       </c>
       <c r="F90">
-        <v>-3.43892434486471</v>
+        <v>-4.04992648443482</v>
       </c>
       <c r="G90">
-        <v>4.380959630543102</v>
+        <v>5.047806129064037</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.70697652740246</v>
       </c>
       <c r="E91">
-        <v>-19.36129797211989</v>
+        <v>-19.08993822415825</v>
       </c>
       <c r="F91">
-        <v>-3.288974934344749</v>
+        <v>-4.042634366187976</v>
       </c>
       <c r="G91">
-        <v>4.330023576875876</v>
+        <v>4.366757390179629</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.043618630023844</v>
       </c>
       <c r="E92">
-        <v>-22.46362418902863</v>
+        <v>-20.35767999413156</v>
       </c>
       <c r="F92">
-        <v>-3.685245190658962</v>
+        <v>-4.699669710699056</v>
       </c>
       <c r="G92">
-        <v>4.432501514044016</v>
+        <v>5.125488080143035</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.483043939391367</v>
       </c>
       <c r="E93">
-        <v>-24.3090362173164</v>
+        <v>-22.69696286922186</v>
       </c>
       <c r="F93">
-        <v>-3.912285785153057</v>
+        <v>-4.470463763814045</v>
       </c>
       <c r="G93">
-        <v>4.453318224394953</v>
+        <v>5.260151141043969</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.008631660762863</v>
       </c>
       <c r="E94">
-        <v>-25.78931738636571</v>
+        <v>-24.94816692486296</v>
       </c>
       <c r="F94">
-        <v>-4.295238378732463</v>
+        <v>-4.609600494625264</v>
       </c>
       <c r="G94">
-        <v>3.631316388084996</v>
+        <v>3.876409316539398</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.611894958999336</v>
       </c>
       <c r="E95">
-        <v>-27.76658952080882</v>
+        <v>-28.63023291270767</v>
       </c>
       <c r="F95">
-        <v>-4.180291632817794</v>
+        <v>-4.92363871886357</v>
       </c>
       <c r="G95">
-        <v>2.382475983760187</v>
+        <v>4.185432189902667</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.289957361504815</v>
       </c>
       <c r="E96">
-        <v>-30.94099319426065</v>
+        <v>-29.32506837902258</v>
       </c>
       <c r="F96">
-        <v>-4.051531032094042</v>
+        <v>-4.851535135021693</v>
       </c>
       <c r="G96">
-        <v>2.426665145618378</v>
+        <v>4.061465501639119</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.012835339037689</v>
       </c>
       <c r="E97">
-        <v>-33.18698044784491</v>
+        <v>-31.54228170876211</v>
       </c>
       <c r="F97">
-        <v>-4.793849285825541</v>
+        <v>-4.797527237093971</v>
       </c>
       <c r="G97">
-        <v>2.313881480186487</v>
+        <v>3.832551209235134</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.782820209775262</v>
       </c>
       <c r="E98">
-        <v>-36.01259652475196</v>
+        <v>-34.58195648777473</v>
       </c>
       <c r="F98">
-        <v>-4.701515313272494</v>
+        <v>-4.961448720596951</v>
       </c>
       <c r="G98">
-        <v>1.10505232924931</v>
+        <v>2.095388785140128</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.56419496807442</v>
       </c>
       <c r="E99">
-        <v>-38.14207067059287</v>
+        <v>-36.95687845330539</v>
       </c>
       <c r="F99">
-        <v>-4.779543380779193</v>
+        <v>-5.491986564128728</v>
       </c>
       <c r="G99">
-        <v>1.38386316402119</v>
+        <v>2.717784588705269</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.375000998666392</v>
       </c>
       <c r="E100">
-        <v>-39.58434662153281</v>
+        <v>-39.13196338935156</v>
       </c>
       <c r="F100">
-        <v>-5.067019175879331</v>
+        <v>-5.648939821039359</v>
       </c>
       <c r="G100">
-        <v>1.085907444395704</v>
+        <v>1.549178566070236</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.137728585298815</v>
       </c>
       <c r="E101">
-        <v>-42.66622904253392</v>
+        <v>-41.73914625826163</v>
       </c>
       <c r="F101">
-        <v>-5.140695001051721</v>
+        <v>-5.822800056641127</v>
       </c>
       <c r="G101">
-        <v>0.8638128758026183</v>
+        <v>1.095766249011654</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.94724995416459</v>
       </c>
       <c r="E102">
-        <v>-43.13452533237813</v>
+        <v>-43.91648184588961</v>
       </c>
       <c r="F102">
-        <v>-5.353138105173683</v>
+        <v>-5.748830989408146</v>
       </c>
       <c r="G102">
-        <v>-0.1696765411926001</v>
+        <v>1.047332967772117</v>
       </c>
     </row>
   </sheetData>
